--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92559929172</v>
+        <v>46157.93063591639</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93063591639</v>
+        <v>46157.93147117615</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93147117615</v>
+        <v>46157.93391677101</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93391677101</v>
+        <v>46157.93704552616</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93704552616</v>
+        <v>46158.28208912073</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28208912073</v>
+        <v>46158.29662680963</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29662680963</v>
+        <v>46158.29800861445</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29800861445</v>
+        <v>46158.33378139978</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33378139978</v>
+        <v>46158.36844557719</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/оборотки за 2025 год/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36844557719</v>
+        <v>46158.37279815862</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
